--- a/reports/devops-jobs-israel-2026-W22.xlsx
+++ b/reports/devops-jobs-israel-2026-W22.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-25T06:38:46</t>
+    <t xml:space="preserve">2026-05-25T10:42:15</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -303,12 +303,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
-  </si>
-  <si>
     <t xml:space="preserve">Production Engineer</t>
   </si>
   <si>
@@ -486,49 +480,385 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4417800793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APRIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4417844995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - JB-652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medulla</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4417800793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4418902824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Beer Sheva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-beer-sheva-at-dell-technologies-4417593597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
   </si>
   <si>
     <t xml:space="preserve">Devops Infra/cloud Engineer</t>
@@ -543,747 +873,411 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
   </si>
   <si>
-    <t xml:space="preserve">Perion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APRIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4417844995</t>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoCompany1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbit Communication Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-malamteam-4392598255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpressVPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
     <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jerusalem District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
   </si>
   <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sayari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - JB-652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
   </si>
   <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; ML Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUNTHEAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-ml-platform-engineer-at-hunthead-4417583856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoCompany1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418656632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Frequency System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - AMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-ams-at-orbit-communication-systems-4418647930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-milestone-systems-4416490430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Hadarly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-hr-hadarly-4418671109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4414866213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering Manager (SRE Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipalti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-team-at-tipalti-4412578041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1299,34 +1293,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
     <t xml:space="preserve">QA Student, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4418656331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-at-algosec-4412544220</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4418693841</t>
   </si>
   <si>
     <t xml:space="preserve">SAP ECC System Administrator</t>
@@ -1344,6 +1317,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
@@ -1353,33 +1347,6 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Technical Support</t>
   </si>
   <si>
@@ -1389,39 +1356,12 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
@@ -1441,9 +1381,6 @@
   </si>
   <si>
     <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1595,7 +1532,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1603,7 +1540,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1611,7 +1548,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -1619,7 +1556,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -1691,7 +1628,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1699,7 +1636,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1718,12 +1655,12 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="B2" s="3">
         <v>44</v>
@@ -1731,31 +1668,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B4" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1774,39 +1711,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>466</v>
+        <v>324</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="B5" s="3">
         <v>24</v>
@@ -1814,15 +1751,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="B7" s="3">
         <v>21</v>
@@ -1830,15 +1767,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>367</v>
+        <v>450</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>470</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
@@ -1846,7 +1783,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
@@ -1854,50 +1791,50 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>368</v>
+        <v>452</v>
       </c>
       <c r="B12" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>473</v>
+        <v>349</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>363</v>
+        <v>453</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>474</v>
+        <v>350</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1922,13 +1859,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2">
@@ -1936,13 +1873,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>14.5</v>
+        <v>15.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1951,88 +1888,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
-        <v>36.1</v>
+        <v>39.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>481</v>
+        <v>460</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.8</v>
+        <v>33.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.5</v>
+        <v>22.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.1</v>
+        <v>16.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2044,8 +1981,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2599,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>56</v>
@@ -2611,126 +2548,126 @@
         <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="J18" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="J20" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>56</v>
@@ -2741,14 +2678,12 @@
       <c r="E22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>112</v>
-      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>41</v>
@@ -2759,26 +2694,28 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>41</v>
@@ -2789,16 +2726,16 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
@@ -2821,10 +2758,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>56</v>
@@ -2833,10 +2770,10 @@
         <v>56</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
@@ -2856,25 +2793,25 @@
         <v>125</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>41</v>
@@ -2885,10 +2822,10 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>55</v>
@@ -2900,13 +2837,13 @@
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
@@ -2917,28 +2854,28 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
@@ -2949,13 +2886,13 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>56</v>
@@ -2964,13 +2901,13 @@
         <v>75</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
@@ -2981,28 +2918,28 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
@@ -3013,13 +2950,13 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>56</v>
@@ -3028,13 +2965,13 @@
         <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
@@ -3045,48 +2982,46 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>146</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J32" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>75</v>
@@ -3096,7 +3031,7 @@
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>44</v>
@@ -3107,13 +3042,13 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>56</v>
@@ -3123,30 +3058,30 @@
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="J34" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>75</v>
@@ -3159,34 +3094,34 @@
         <v>157</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>159</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>62</v>
@@ -3197,16 +3132,16 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>162</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>75</v>
@@ -3216,24 +3151,24 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>56</v>
@@ -3246,27 +3181,27 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>75</v>
@@ -3276,27 +3211,27 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>75</v>
@@ -3306,24 +3241,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>56</v>
@@ -3336,27 +3271,27 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="J41" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>75</v>
@@ -3366,27 +3301,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>75</v>
@@ -3396,30 +3331,30 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J43" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>185</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3429,54 +3364,54 @@
         <v>186</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>75</v>
@@ -3486,10 +3421,10 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J46" s="3">
         <v>6</v>
@@ -3497,16 +3432,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>75</v>
@@ -3516,10 +3451,10 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J47" s="3">
         <v>6</v>
@@ -3527,13 +3462,13 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>56</v>
@@ -3546,7 +3481,7 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>62</v>
@@ -3557,13 +3492,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
@@ -3576,7 +3511,7 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>84</v>
@@ -3587,13 +3522,13 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
@@ -3606,27 +3541,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>75</v>
@@ -3636,10 +3571,10 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="J51" s="3">
         <v>4</v>
@@ -3647,13 +3582,13 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
@@ -3669,7 +3604,7 @@
         <v>212</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="J52" s="3">
         <v>5</v>
@@ -3683,10 +3618,10 @@
         <v>214</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>75</v>
@@ -3699,51 +3634,51 @@
         <v>215</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>63</v>
+        <v>161</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
@@ -3759,21 +3694,21 @@
         <v>219</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>220</v>
+        <v>63</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
@@ -3786,114 +3721,114 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="J56" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>225</v>
+        <v>63</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>230</v>
+        <v>63</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>56</v>
@@ -3906,54 +3841,54 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>233</v>
+        <v>108</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="J61" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>56</v>
@@ -3961,32 +3896,34 @@
       <c r="E62" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="J62" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>75</v>
@@ -3996,27 +3933,27 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>245</v>
+        <v>174</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -4026,24 +3963,24 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>56</v>
@@ -4056,54 +3993,54 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>63</v>
+        <v>245</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="J66" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>56</v>
@@ -4116,7 +4053,7 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>84</v>
@@ -4127,119 +4064,119 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="J70" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>63</v>
+        <v>259</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="J71" s="3">
         <v>5</v>
@@ -4247,7 +4184,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>110</v>
+        <v>263</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>264</v>
@@ -4256,10 +4193,10 @@
         <v>265</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
@@ -4269,10 +4206,10 @@
         <v>266</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -4280,10 +4217,10 @@
         <v>267</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>160</v>
+        <v>233</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>56</v>
@@ -4296,30 +4233,30 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="J73" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>270</v>
+        <v>154</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
@@ -4329,51 +4266,51 @@
         <v>271</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>160</v>
+        <v>233</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
@@ -4386,57 +4323,57 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="J76" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="J77" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>75</v>
@@ -4446,27 +4383,27 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>282</v>
+        <v>173</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>160</v>
+        <v>285</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>75</v>
@@ -4476,57 +4413,57 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>75</v>
@@ -4536,10 +4473,10 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="J81" s="3">
         <v>3</v>
@@ -4547,13 +4484,13 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>56</v>
@@ -4566,10 +4503,10 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J82" s="3">
         <v>6</v>
@@ -4577,16 +4514,16 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>172</v>
+        <v>282</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>75</v>
@@ -4596,7 +4533,7 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>84</v>
@@ -4607,16 +4544,16 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>155</v>
+        <v>300</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>75</v>
@@ -4626,27 +4563,27 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>75</v>
@@ -4656,10 +4593,10 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="J85" s="3">
         <v>5</v>
@@ -4667,16 +4604,16 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>75</v>
@@ -4686,27 +4623,27 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="J86" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>75</v>
@@ -4716,27 +4653,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="J87" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>312</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>293</v>
+        <v>195</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>75</v>
@@ -4757,16 +4694,16 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="D89" s="3" t="s">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>75</v>
@@ -4779,24 +4716,24 @@
         <v>316</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="J89" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>317</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>75</v>
@@ -4809,144 +4746,146 @@
         <v>318</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>306</v>
+        <v>163</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="J91" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>249</v>
+        <v>323</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>322</v>
+        <v>181</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="J92" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>325</v>
+        <v>268</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>156</v>
+        <v>327</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>75</v>
+        <v>328</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="J93" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>328</v>
+        <v>251</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J94" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>330</v>
+        <v>268</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>178</v>
+        <v>333</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>75</v>
@@ -4956,27 +4895,27 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>75</v>
@@ -4986,287 +4925,107 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>249</v>
+        <v>338</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>334</v>
+        <v>154</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>337</v>
+        <v>251</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J98" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="J99" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J100" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J102" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J103" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J104" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J105" s="3">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5366,12 +5125,6 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
-    <hyperlink ref="H105" r:id="rId104"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5379,7 +5132,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -5432,13 +5185,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5446,18 +5199,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5465,18 +5218,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5484,18 +5237,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5503,18 +5256,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5522,18 +5275,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>110</v>
+        <v>213</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5541,18 +5294,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5560,18 +5313,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5579,11 +5332,68 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>284</v>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5594,6 +5404,9 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5607,15 +5420,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>361</v>
+        <v>234</v>
       </c>
       <c r="B2" s="3">
         <v>22</v>
@@ -5623,79 +5436,79 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -5703,34 +5516,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5749,7 +5562,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
@@ -5770,7 +5583,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5778,7 +5591,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5786,7 +5599,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5794,7 +5607,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5818,7 +5631,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5826,7 +5639,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5834,7 +5647,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5842,7 +5655,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5850,7 +5663,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5858,7 +5671,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5866,7 +5679,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5887,16 +5700,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
@@ -5932,7 +5745,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C4" s="3">
         <v>14.0</v>
@@ -5946,7 +5759,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3">
         <v>11.3</v>
@@ -5960,10 +5773,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3">
-        <v>7.2</v>
+        <v>7.0</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5974,10 +5787,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5988,10 +5801,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0</v>
+        <v>5.8</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6002,13 +5815,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>128</v>
+        <v>268</v>
       </c>
       <c r="C9" s="3">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6016,10 +5829,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -6030,13 +5843,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>249</v>
+        <v>109</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6044,13 +5857,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6058,7 +5871,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6072,10 +5885,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>234</v>
+        <v>323</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6086,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6100,7 +5913,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6126,15 +5939,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6148,10 +5961,10 @@
         <v>75</v>
       </c>
       <c r="B3" s="3">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4">
@@ -6159,10 +5972,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6181,7 +5994,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
@@ -6189,20 +6002,20 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6210,7 +6023,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6218,31 +6031,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6269,10 +6082,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6284,10 +6097,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6304,28 +6117,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>387</v>
+        <v>70</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6336,31 +6149,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>293</v>
+        <v>154</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -6368,31 +6181,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>278</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>211</v>
+        <v>381</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="F4" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>181</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -6400,31 +6213,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>228</v>
+        <v>385</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>400</v>
+        <v>294</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="6">
@@ -6432,31 +6245,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>403</v>
+        <v>335</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
@@ -6464,31 +6277,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>408</v>
+        <v>335</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>409</v>
+        <v>323</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="F7" s="3">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>412</v>
+        <v>336</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
@@ -6496,31 +6309,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>414</v>
+        <v>251</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>160</v>
+        <v>394</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
@@ -6528,31 +6341,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>177</v>
+        <v>398</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F9" s="3">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -6560,31 +6373,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>324</v>
+        <v>402</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>280</v>
+        <v>403</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>181</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -6592,31 +6405,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -6624,31 +6437,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>427</v>
+        <v>206</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>322</v>
+        <v>181</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6656,31 +6469,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>430</v>
+        <v>335</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
@@ -6688,31 +6501,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -6720,28 +6533,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>438</v>
+        <v>154</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -6752,31 +6565,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -6784,28 +6597,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>211</v>
+        <v>429</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -6816,31 +6629,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>449</v>
+        <v>248</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>450</v>
+        <v>154</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
@@ -6848,31 +6661,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>35</v>
+        <v>436</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -6880,28 +6693,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>457</v>
+        <v>133</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -6912,28 +6725,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>461</v>
+        <v>35</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W22.xlsx
+++ b/reports/devops-jobs-israel-2026-W22.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-25T10:42:15</t>
+    <t xml:space="preserve">2026-05-26T10:15:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0%</t>
+    <t xml:space="preserve">1.8%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -165,12 +165,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4857059101?gh_jid=4857059101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tech Lead DevOps Engineer</t>
   </si>
   <si>
@@ -276,6 +270,18 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
     <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
   </si>
   <si>
@@ -303,6 +309,18 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668079006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Engineer</t>
   </si>
   <si>
@@ -480,6 +498,18 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
@@ -489,828 +519,816 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
     <t xml:space="preserve">4M Analytics</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4417800793</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentic DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empire Media Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/agentic-devops-at-empire-media-network-4418951731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sequoia Capital Global Equities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-sequoia-capital-global-equities-4419140371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Beer Sheva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-beer-sheva-at-dell-technologies-4417593597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - JB-652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; ML Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUNTHEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-ml-platform-engineer-at-hunthead-4417583856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Software Engineer - SAP Cloud Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-software-engineer-sap-cloud-virtualization-at-sap-4417871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4414852297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Azure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-azure-at-varonis-4401302225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Semiconductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4417076579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbit Communication Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-malamteam-4392598255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - AMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-ams-at-orbit-communication-systems-4418647930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4414866213</t>
+  </si>
+  <si>
     <t xml:space="preserve">SRE / DevOps Lead</t>
   </si>
   <si>
-    <t xml:space="preserve">APRIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4417844995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sayari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - JB-652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4418902824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Beer Sheva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dell Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-beer-sheva-at-dell-technologies-4417593597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoCompany1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-malamteam-4392598255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netoplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-netoplay-4418933911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InspHire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpressVPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Student, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4418693841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -1356,21 +1374,105 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
   </si>
   <si>
+    <t xml:space="preserve">CAD Engineering - Student position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -1380,7 +1482,7 @@
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform/IaC</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1532,7 +1634,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
@@ -1540,7 +1642,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1548,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -1556,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1564,7 +1666,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1628,7 +1730,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -1636,7 +1738,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1655,44 +1757,44 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>435</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1711,130 +1813,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>481</v>
       </c>
       <c r="B4" s="3">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>447</v>
+        <v>331</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>450</v>
+        <v>384</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>484</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>451</v>
+        <v>300</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>354</v>
+        <v>485</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1859,13 +1961,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2">
@@ -1873,13 +1975,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3">
-        <v>15.2</v>
+        <v>13.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1888,88 +1990,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
-        <v>39.9</v>
+        <v>36.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>8.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.8</v>
+        <v>32.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>22.4</v>
+        <v>17.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1982,7 +2084,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2053,7 +2155,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2085,7 +2187,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2117,7 +2219,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2136,134 +2238,136 @@
       <c r="E5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
@@ -2275,7 +2379,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -2283,434 +2387,434 @@
         <v>67</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J13" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J17" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J18" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="J21" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
@@ -2721,88 +2825,88 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>127</v>
@@ -2811,410 +2915,412 @@
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>148</v>
+        <v>54</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J33" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="J39" s="3">
         <v>0</v>
@@ -3222,89 +3328,89 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="J42" s="3">
         <v>6</v>
@@ -3312,319 +3418,321 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>196</v>
+        <v>54</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>208</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>210</v>
+        <v>114</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="J52" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3634,114 +3742,114 @@
         <v>215</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D55" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>63</v>
+        <v>222</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>171</v>
+        <v>224</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3751,27 +3859,27 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3781,57 +3889,57 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
       <c r="J59" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3841,612 +3949,610 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>108</v>
+        <v>238</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>234</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>240</v>
+        <v>114</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>56</v>
+        <v>249</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="J64" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>56</v>
+        <v>249</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>251</v>
+        <v>180</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="J69" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>154</v>
+        <v>266</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="J72" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>267</v>
+        <v>65</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>233</v>
+        <v>164</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="J73" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="J74" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="J75" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>282</v>
+        <v>173</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="J78" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="J80" s="3">
         <v>1</v>
@@ -4454,361 +4560,361 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>288</v>
+        <v>61</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>290</v>
+        <v>185</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>292</v>
+        <v>114</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>294</v>
+        <v>188</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F83" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>301</v>
+        <v>188</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>303</v>
+        <v>159</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>304</v>
+        <v>188</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="J85" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>163</v>
+        <v>299</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>196</v>
+        <v>124</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>118</v>
+        <v>318</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>323</v>
+        <v>234</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>181</v>
+        <v>326</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>324</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="J92" s="3">
         <v>0</v>
@@ -4816,29 +4922,31 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>268</v>
+        <v>330</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>327</v>
+        <v>160</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F93" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>331</v>
+      </c>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="J93" s="3">
         <v>1</v>
@@ -4846,89 +4954,89 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>154</v>
+        <v>326</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>327</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="J94" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>333</v>
+        <v>248</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>166</v>
+        <v>60</v>
       </c>
       <c r="J95" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>323</v>
+        <v>220</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="J96" s="3">
         <v>5</v>
@@ -4936,96 +5044,426 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J97" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>118</v>
+        <v>318</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="J98" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>343</v>
+        <v>307</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="J99" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J100" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J101" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J103" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J104" s="3">
         <v>5</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J105" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J106" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J107" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J108" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J109" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J110" s="3">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J110"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5125,6 +5563,17 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5132,9 +5581,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5166,13 +5615,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5180,18 +5629,18 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5199,18 +5648,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5218,18 +5667,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5237,18 +5686,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5256,18 +5705,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5275,18 +5724,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5294,18 +5743,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5313,18 +5762,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5332,18 +5781,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>299</v>
+        <v>114</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5351,18 +5800,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>319</v>
+        <v>114</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>320</v>
+        <v>262</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5370,18 +5819,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>321</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5389,11 +5838,125 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
         <v>325</v>
       </c>
+      <c r="B17" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>365</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G19"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5407,6 +5970,12 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5420,95 +5989,95 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -5516,34 +6085,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5562,15 +6131,15 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -5578,12 +6147,12 @@
         <v>35</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5591,7 +6160,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5599,7 +6168,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5607,7 +6176,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5615,7 +6184,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5623,7 +6192,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5631,7 +6200,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5639,7 +6208,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5647,7 +6216,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5655,7 +6224,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5663,7 +6232,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5671,7 +6240,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5679,7 +6248,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5700,16 +6269,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
@@ -5717,13 +6286,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3">
-        <v>18.5</v>
+        <v>23.5</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -5731,13 +6300,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3">
-        <v>15.6</v>
+        <v>14.0</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5745,10 +6314,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
-        <v>14.0</v>
+        <v>12.5</v>
       </c>
       <c r="D4" s="3">
         <v>4</v>
@@ -5759,7 +6328,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C5" s="3">
         <v>11.3</v>
@@ -5773,10 +6342,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C6" s="3">
-        <v>7.0</v>
+        <v>7.2</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5787,10 +6356,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5801,10 +6370,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -5815,13 +6384,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>132</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5829,10 +6398,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -5843,13 +6412,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5857,13 +6426,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5871,10 +6440,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>206</v>
+        <v>330</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -5885,10 +6454,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>323</v>
+        <v>159</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5899,7 +6468,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5913,7 +6482,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5939,18 +6508,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5958,13 +6527,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4">
@@ -5972,10 +6541,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5994,28 +6563,28 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6023,7 +6592,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6031,15 +6600,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6047,15 +6616,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>100</v>
+        <v>318</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6082,10 +6651,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6097,10 +6666,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6117,28 +6686,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6149,28 +6718,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>44</v>
@@ -6181,31 +6750,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>278</v>
+        <v>411</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>381</v>
+        <v>317</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>382</v>
+        <v>413</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>383</v>
+        <v>414</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -6213,31 +6782,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>384</v>
+        <v>415</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>294</v>
+        <v>164</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -6245,31 +6814,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>335</v>
+        <v>419</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>389</v>
+        <v>207</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -6277,31 +6846,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>335</v>
+        <v>422</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>392</v>
+        <v>425</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -6309,31 +6878,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>251</v>
+        <v>428</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -6341,31 +6910,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>195</v>
+        <v>434</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -6373,31 +6942,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>372</v>
-      </c>
       <c r="F10" s="3">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -6405,31 +6974,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -6437,31 +7006,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>384</v>
+        <v>445</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="F12" s="3">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -6469,31 +7038,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>335</v>
+        <v>448</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>412</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -6501,31 +7070,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F14" s="3">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -6533,28 +7102,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="F15" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>422</v>
+        <v>457</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -6565,31 +7134,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>214</v>
+        <v>460</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -6597,28 +7166,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>428</v>
+        <v>207</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>429</v>
+        <v>164</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -6629,31 +7198,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>248</v>
+        <v>467</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
@@ -6661,31 +7230,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>181</v>
+        <v>277</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20">
@@ -6693,31 +7262,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>439</v>
+        <v>351</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>472</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21">
@@ -6725,28 +7294,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>35</v>
+        <v>476</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W22.xlsx
+++ b/reports/devops-jobs-israel-2026-W22.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-26T10:15:03</t>
+    <t xml:space="preserve">2026-05-27T10:14:29</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8%</t>
+    <t xml:space="preserve">2.8%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -258,244 +258,361 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
   </si>
   <si>
-    <t xml:space="preserve">GenAI Automation Engineer, Competitive Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security, Rust, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7939091&amp;gh_jid=7939091</t>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668079006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontend Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-7635287?gh_jid=7635287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Helm, Istio, Service Mesh, Security, Argo CD, Observability, Karpenter, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8323401002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineering (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, Linux, Python, CDK, Networking, Security, FinOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7747977003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Group Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razel Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-razel-group-4419802735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Data Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-engineer-at-compie-technologies-4419815090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - JB-652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668079006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frontend Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-7635287?gh_jid=7635287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Helm, Istio, Service Mesh, Security, Argo CD, Observability, Karpenter, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8323401002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Group Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
   </si>
   <si>
     <t xml:space="preserve">Medulla</t>
@@ -510,15 +627,6 @@
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco</t>
   </si>
   <si>
@@ -531,19 +639,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
   </si>
   <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4417800793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
     <t xml:space="preserve">Fiverr</t>
@@ -561,13 +687,442 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
   </si>
   <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-compie-pro-4416804884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grip Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; ML Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUNTHEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-ml-platform-engineer-at-hunthead-4417583856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-native-4418239509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Cloud Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-platform-at-monday-com-4419824552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Azure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-azure-at-varonis-4401302225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4414852297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CRM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-crm-at-monday-com-4419805943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbit Communication Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4416822105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-mayfield-4419119918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InspHire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpressVPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4418564684</t>
   </si>
   <si>
     <t xml:space="preserve">Agentic DevOps</t>
@@ -576,715 +1131,205 @@
     <t xml:space="preserve">Empire Media Network</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/agentic-devops-at-empire-media-network-4418951731</t>
   </si>
   <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sequoia Capital Global Equities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-sequoia-capital-global-equities-4419140371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Beer Sheva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dell Technologies</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
   </si>
   <si>
     <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-beer-sheva-at-dell-technologies-4417593597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sayari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - JB-652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; ML Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUNTHEAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-ml-platform-engineer-at-hunthead-4417583856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Software Engineer - SAP Cloud Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-software-engineer-sap-cloud-virtualization-at-sap-4417871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4414852297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Azure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-azure-at-varonis-4401302225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4417076579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-malamteam-4392598255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - AMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-ams-at-orbit-communication-systems-4418647930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4414866213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netoplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-netoplay-4418933911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InspHire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
@@ -1308,15 +1353,24 @@
     <t xml:space="preserve">Intel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
   </si>
   <si>
+    <t xml:space="preserve">QA Student, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4419112669</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAP ECC System Administrator</t>
   </si>
   <si>
@@ -1326,9 +1380,6 @@
     <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -1365,97 +1416,31 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAD Engineering - Student position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2 Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1464,22 +1449,25 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -1634,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -1642,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -1650,7 +1638,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -1658,7 +1646,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>312</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1666,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1730,7 +1718,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1738,7 +1726,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1757,36 +1745,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>435</v>
+        <v>406</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1794,7 +1782,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1813,130 +1801,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>481</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>483</v>
+        <v>378</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>384</v>
+        <v>478</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>486</v>
+        <v>304</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>487</v>
+        <v>374</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>382</v>
+        <v>483</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1961,13 +1949,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2">
@@ -1975,13 +1963,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1990,34 +1978,34 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3">
-        <v>36.8</v>
+        <v>37.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.2</v>
+        <v>8.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -2026,28 +2014,28 @@
         <v>3.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.6</v>
+        <v>34.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -2056,22 +2044,22 @@
         <v>17.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>13.4</v>
+        <v>16.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2155,7 +2143,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2187,7 +2175,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2219,7 +2207,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -2251,7 +2239,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -2283,7 +2271,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2315,7 +2303,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2347,7 +2335,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -2379,7 +2367,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2411,7 +2399,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -2443,7 +2431,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -2475,7 +2463,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -2486,7 +2474,7 @@
         <v>68</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>54</v>
@@ -2495,19 +2483,19 @@
         <v>73</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -2518,7 +2506,7 @@
         <v>68</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>54</v>
@@ -2527,24 +2515,24 @@
         <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>68</v>
@@ -2556,33 +2544,33 @@
         <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>54</v>
@@ -2600,10 +2588,10 @@
         <v>91</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J16" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -2611,7 +2599,7 @@
         <v>92</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>54</v>
@@ -2623,19 +2611,19 @@
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J17" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2643,7 +2631,7 @@
         <v>96</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>54</v>
@@ -2652,103 +2640,103 @@
         <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>112</v>
@@ -2760,10 +2748,10 @@
         <v>113</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -2782,90 +2770,90 @@
       <c r="E22" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>116</v>
-      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>54</v>
@@ -2874,62 +2862,62 @@
         <v>54</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="J26" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>53</v>
@@ -2941,27 +2929,27 @@
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>53</v>
@@ -2973,30 +2961,30 @@
         <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>54</v>
@@ -3005,30 +2993,30 @@
         <v>73</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>54</v>
@@ -3037,30 +3025,30 @@
         <v>73</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>54</v>
@@ -3069,40 +3057,38 @@
         <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
@@ -3110,10 +3096,10 @@
         <v>151</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="J32" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3121,43 +3107,45 @@
         <v>152</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>73</v>
@@ -3173,48 +3161,48 @@
         <v>44</v>
       </c>
       <c r="J34" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>161</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>54</v>
@@ -3227,27 +3215,27 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>73</v>
@@ -3257,27 +3245,27 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>73</v>
@@ -3290,24 +3278,24 @@
         <v>171</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J38" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>73</v>
@@ -3320,24 +3308,24 @@
         <v>174</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>175</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>73</v>
@@ -3347,27 +3335,27 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>178</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>73</v>
@@ -3377,24 +3365,24 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="J41" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>54</v>
@@ -3407,24 +3395,24 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>54</v>
@@ -3437,149 +3425,147 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D46" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="3"/>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="I47" s="3" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>73</v>
@@ -3589,27 +3575,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>73</v>
@@ -3622,21 +3608,21 @@
         <v>205</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>54</v>
@@ -3649,13 +3635,13 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -3666,7 +3652,7 @@
         <v>210</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>54</v>
@@ -3682,21 +3668,21 @@
         <v>211</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>54</v>
@@ -3709,27 +3695,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>73</v>
@@ -3739,24 +3725,24 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>54</v>
@@ -3772,27 +3758,27 @@
         <v>218</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3802,7 +3788,7 @@
         <v>221</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="J55" s="3">
         <v>5</v>
@@ -3816,10 +3802,10 @@
         <v>223</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>73</v>
@@ -3829,10 +3815,10 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="J56" s="3">
         <v>6</v>
@@ -3840,46 +3826,46 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="D58" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3889,84 +3875,84 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>233</v>
+        <v>152</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="J60" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>54</v>
@@ -3974,32 +3960,34 @@
       <c r="E61" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>114</v>
+        <v>240</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>241</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>242</v>
+        <v>166</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>73</v>
@@ -4009,24 +3997,24 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="C63" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>54</v>
@@ -4039,40 +4027,40 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>249</v>
+        <v>120</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="J64" s="3">
         <v>0</v>
@@ -4080,13 +4068,13 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>54</v>
@@ -4099,24 +4087,24 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>54</v>
@@ -4129,114 +4117,114 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>248</v>
+        <v>163</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>249</v>
+        <v>54</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="J67" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="J68" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="D69" s="3" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>265</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>54</v>
@@ -4249,117 +4237,117 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>244</v>
+        <v>61</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>242</v>
+        <v>166</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="J72" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>65</v>
+        <v>209</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>275</v>
+        <v>194</v>
       </c>
       <c r="J73" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>73</v>
@@ -4369,27 +4357,27 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="J74" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>73</v>
@@ -4399,27 +4387,27 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>73</v>
@@ -4429,24 +4417,24 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="J76" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>54</v>
@@ -4459,27 +4447,27 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>73</v>
@@ -4489,54 +4477,56 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>290</v>
+        <v>166</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F79" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>54</v>
@@ -4549,54 +4539,54 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>61</v>
+        <v>290</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>54</v>
@@ -4609,42 +4599,40 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>300</v>
-      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -4652,13 +4640,13 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>54</v>
@@ -4671,10 +4659,10 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="J84" s="3">
         <v>0</v>
@@ -4682,13 +4670,13 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>159</v>
+        <v>302</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>188</v>
+        <v>303</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>54</v>
@@ -4696,15 +4684,17 @@
       <c r="E85" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="J85" s="3">
         <v>1</v>
@@ -4712,16 +4702,16 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>309</v>
+        <v>166</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>73</v>
@@ -4731,24 +4721,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="J86" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>311</v>
+        <v>110</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>299</v>
+        <v>163</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>54</v>
@@ -4761,27 +4751,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>73</v>
@@ -4791,27 +4781,27 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>316</v>
+        <v>198</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>317</v>
+        <v>163</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>318</v>
+        <v>54</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>73</v>
@@ -4821,10 +4811,10 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="J89" s="3">
         <v>2</v>
@@ -4832,16 +4822,16 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>73</v>
@@ -4851,27 +4841,27 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>309</v>
+        <v>169</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>73</v>
@@ -4881,10 +4871,10 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="J91" s="3">
         <v>5</v>
@@ -4892,168 +4882,168 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>54</v>
+        <v>322</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>327</v>
+        <v>73</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>160</v>
+        <v>325</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>331</v>
-      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>60</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>327</v>
+        <v>129</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>249</v>
+        <v>120</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F95" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>332</v>
+      </c>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>60</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>220</v>
+        <v>334</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>164</v>
+        <v>335</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="J96" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>164</v>
+        <v>335</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>73</v>
@@ -5063,130 +5053,130 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="J97" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>316</v>
+        <v>265</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>318</v>
+        <v>54</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="J98" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>277</v>
+        <v>166</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J99" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>349</v>
+        <v>166</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="J100" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="J101" s="3">
         <v>6</v>
@@ -5194,13 +5184,13 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>192</v>
+        <v>349</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>164</v>
+        <v>303</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>54</v>
@@ -5213,54 +5203,54 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>188</v>
+        <v>354</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="J103" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>358</v>
+        <v>227</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>54</v>
@@ -5273,87 +5263,87 @@
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J104" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>361</v>
+        <v>264</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="J105" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>233</v>
+        <v>360</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>277</v>
+        <v>166</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>99</v>
+        <v>219</v>
       </c>
       <c r="J106" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>367</v>
+        <v>255</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>277</v>
+        <v>364</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>38</v>
@@ -5363,107 +5353,77 @@
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="J107" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>61</v>
+        <v>222</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="J108" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="J109" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J110" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J110"/>
+  <autoFilter ref="A1:J109"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5573,7 +5533,6 @@
     <hyperlink ref="H107" r:id="rId106"/>
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
-    <hyperlink ref="H110" r:id="rId109"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5581,9 +5540,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5615,13 +5574,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5629,37 +5588,37 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5667,18 +5626,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>110</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5686,18 +5645,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5705,18 +5664,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5724,18 +5683,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5743,18 +5702,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5762,18 +5721,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5781,18 +5740,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>269</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>248</v>
+        <v>163</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5800,18 +5759,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>114</v>
+        <v>277</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>263</v>
+        <v>163</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5819,18 +5778,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>287</v>
+        <v>173</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5843,13 +5802,13 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>114</v>
+        <v>295</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>188</v>
+        <v>296</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5857,18 +5816,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>299</v>
+        <v>166</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5876,18 +5835,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5895,18 +5854,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>326</v>
+        <v>166</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -5914,18 +5873,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>164</v>
+        <v>335</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5933,18 +5892,18 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>233</v>
+        <v>341</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>277</v>
+        <v>166</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -5952,11 +5911,68 @@
         <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>365</v>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G22"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5976,6 +5992,9 @@
     <hyperlink ref="G17" r:id="rId16"/>
     <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5989,23 +6008,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B3" s="3">
         <v>23</v>
@@ -6013,7 +6032,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
@@ -6021,7 +6040,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -6029,7 +6048,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B6" s="3">
         <v>17</v>
@@ -6037,7 +6056,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B7" s="3">
         <v>16</v>
@@ -6045,7 +6064,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B8" s="3">
         <v>15</v>
@@ -6053,7 +6072,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
@@ -6061,7 +6080,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -6069,23 +6088,23 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -6093,15 +6112,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6109,7 +6128,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6131,7 +6150,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -6139,20 +6158,20 @@
         <v>68</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6160,15 +6179,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>265</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6176,7 +6195,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6184,15 +6203,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>52</v>
+        <v>299</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6200,7 +6219,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6208,7 +6227,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6216,7 +6235,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6224,7 +6243,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6232,7 +6251,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6240,7 +6259,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6248,7 +6267,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6269,16 +6288,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -6289,10 +6308,10 @@
         <v>68</v>
       </c>
       <c r="C2" s="3">
-        <v>23.5</v>
+        <v>18.5</v>
       </c>
       <c r="D2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -6300,13 +6319,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3">
-        <v>14.0</v>
+        <v>17.5</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6314,13 +6333,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="C4" s="3">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6328,13 +6347,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6342,13 +6361,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C6" s="3">
-        <v>7.2</v>
+        <v>11.3</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6356,10 +6375,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C7" s="3">
-        <v>7.0</v>
+        <v>7.2</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6370,10 +6389,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6384,10 +6403,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6398,13 +6417,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -6412,7 +6431,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -6426,13 +6445,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6440,13 +6459,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>330</v>
+        <v>111</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6454,7 +6473,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -6468,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6482,7 +6501,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6508,18 +6527,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>327</v>
+        <v>129</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6530,10 +6549,10 @@
         <v>73</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -6541,10 +6560,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6563,7 +6582,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -6571,15 +6590,15 @@
         <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -6587,28 +6606,28 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6616,15 +6635,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>318</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6651,10 +6670,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6666,10 +6685,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6686,7 +6705,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>68</v>
@@ -6695,19 +6714,19 @@
         <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6718,28 +6737,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>44</v>
@@ -6750,31 +6769,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5">
@@ -6782,31 +6801,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>416</v>
+        <v>331</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F5" s="3">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6">
@@ -6814,31 +6833,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>164</v>
+        <v>413</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="F6" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
@@ -6846,31 +6865,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>422</v>
+        <v>330</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>423</v>
+        <v>331</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>426</v>
+        <v>333</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -6878,31 +6897,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>429</v>
+        <v>321</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
@@ -6910,28 +6929,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>434</v>
+        <v>166</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>435</v>
+        <v>396</v>
       </c>
       <c r="F9" s="3">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -6942,31 +6961,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="F10" s="3">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11">
@@ -6974,31 +6993,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>435</v>
+        <v>406</v>
       </c>
       <c r="F11" s="3">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -7006,31 +7025,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>139</v>
+        <v>433</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>140</v>
+        <v>434</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -7038,28 +7057,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>438</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7070,31 +7089,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>173</v>
+        <v>296</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15">
@@ -7102,31 +7121,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -7134,28 +7153,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>164</v>
+        <v>452</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7166,31 +7185,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18">
@@ -7198,31 +7217,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>277</v>
+        <v>199</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F18" s="3">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -7230,31 +7249,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>467</v>
+        <v>140</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>275</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -7262,31 +7281,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>351</v>
+        <v>465</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>435</v>
+        <v>396</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>275</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -7294,28 +7313,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>164</v>
+        <v>471</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W22.xlsx
+++ b/reports/devops-jobs-israel-2026-W22.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-27T10:14:29</t>
+    <t xml:space="preserve">2026-05-28T10:21:13</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8%</t>
+    <t xml:space="preserve">2.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -309,6 +309,18 @@
     <t xml:space="preserve">2026-05-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Engineer</t>
   </si>
   <si>
@@ -324,6 +336,15 @@
     <t xml:space="preserve">2026-05-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
     <t xml:space="preserve">Appsflyer</t>
   </si>
   <si>
@@ -471,12 +492,6 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
@@ -498,6 +513,18 @@
     <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
   </si>
   <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
     <t xml:space="preserve">Product Team Leader</t>
   </si>
   <si>
@@ -507,43 +534,58 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
-    <t xml:space="preserve">Razel Group</t>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-razel-group-4419802735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
   </si>
   <si>
     <t xml:space="preserve">Glassbox</t>
@@ -555,13 +597,40 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
   </si>
   <si>
     <t xml:space="preserve">Buildots</t>
@@ -570,6 +639,303 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
   </si>
   <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417214194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grip Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4417624412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4420235343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4419851508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4420267483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Cloud Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-platform-at-monday-com-4419824552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-mobileye-4409774817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-mayfield-4419119918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4419826411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - JB-652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sayari</t>
   </si>
   <si>
@@ -585,13 +951,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-engineer-at-compie-technologies-4419815090</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer - JB-652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-unilink-ltd-4419879717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
   </si>
   <si>
     <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
@@ -603,577 +978,274 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CRM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-crm-at-monday-com-4419805943</t>
   </si>
   <si>
     <t xml:space="preserve">Medulla</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshed Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-eshed-group-4417626050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4418249612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-malamteam-4392598255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4415208513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377765290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4414866213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InspHire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netoplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-netoplay-4418933911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Lead</t>
   </si>
   <si>
-    <t xml:space="preserve">Compie Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-compie-pro-4416804884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grip Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; ML Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUNTHEAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-ml-platform-engineer-at-hunthead-4417583856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-native-4418239509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Cloud Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-platform-at-monday-com-4419824552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Azure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+    <t xml:space="preserve">Corsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpressVPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-azure-at-varonis-4401302225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4414852297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CRM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-crm-at-monday-com-4419805943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4416822105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mayfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-mayfield-4419119918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InspHire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4418564684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agentic DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empire Media Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/agentic-devops-at-empire-media-network-4418951731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform</t>
+    <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
     <t xml:space="preserve">Helm</t>
   </si>
   <si>
-    <t xml:space="preserve">Prometheus</t>
+    <t xml:space="preserve">WAF/CDN</t>
   </si>
   <si>
     <t xml:space="preserve">Open Roles</t>
@@ -1191,10 +1263,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3%</t>
+    <t xml:space="preserve">64.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1257,18 +1329,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1287,18 +1347,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation student- Jerusalem</t>
   </si>
   <si>
@@ -1308,9 +1356,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1323,9 +1368,6 @@
     <t xml:space="preserve">Ben-Gurion University of the Negev</t>
   </si>
   <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
   </si>
   <si>
@@ -1359,18 +1401,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Student, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4419112669</t>
-  </si>
-  <si>
     <t xml:space="preserve">SAP ECC System Administrator</t>
   </si>
   <si>
@@ -1386,15 +1416,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator (36311)</t>
   </si>
   <si>
@@ -1443,6 +1464,48 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAD Engineering - Student position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1452,12 +1515,12 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
@@ -1465,9 +1528,6 @@
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -1622,7 +1682,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
@@ -1630,7 +1690,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -1638,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1646,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>333</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -1718,7 +1778,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
@@ -1726,7 +1786,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1745,20 +1805,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -1766,15 +1826,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1782,7 +1842,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1801,71 +1861,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="B2" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>332</v>
+        <v>497</v>
       </c>
       <c r="B4" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>476</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>477</v>
+        <v>402</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>378</v>
+        <v>498</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
@@ -1873,58 +1933,58 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>481</v>
+        <v>401</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>304</v>
+        <v>502</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1949,13 +2009,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2">
@@ -1963,13 +2023,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1978,88 +2038,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3">
-        <v>37.1</v>
+        <v>37.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.7</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.2</v>
+        <v>31.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.2</v>
+        <v>14.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2143,7 +2203,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2175,7 +2235,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2207,7 +2267,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -2239,7 +2299,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -2271,7 +2331,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -2303,7 +2363,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2335,7 +2395,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -2367,7 +2427,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2399,7 +2459,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -2431,7 +2491,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -2463,7 +2523,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2555,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -2527,7 +2587,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -2559,7 +2619,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -2591,7 +2651,7 @@
         <v>44</v>
       </c>
       <c r="J16" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -2623,7 +2683,7 @@
         <v>95</v>
       </c>
       <c r="J17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -2631,63 +2691,63 @@
         <v>96</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J18" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J19" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2695,10 +2755,10 @@
         <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>54</v>
@@ -2707,70 +2767,72 @@
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J20" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2778,10 +2840,10 @@
         <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="J22" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -2792,36 +2854,36 @@
         <v>118</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>54</v>
@@ -2830,71 +2892,69 @@
         <v>54</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>123</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>130</v>
@@ -2906,50 +2966,50 @@
         <v>131</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>53</v>
@@ -2958,7 +3018,7 @@
         <v>54</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>137</v>
@@ -2970,117 +3030,117 @@
         <v>138</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="J28" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>54</v>
@@ -3088,29 +3148,31 @@
       <c r="E32" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>54</v>
@@ -3119,63 +3181,65 @@
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>73</v>
@@ -3185,40 +3249,42 @@
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J35" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J36" s="3">
         <v>0</v>
@@ -3226,13 +3292,13 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>54</v>
@@ -3242,30 +3308,30 @@
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>73</v>
@@ -3275,27 +3341,27 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>73</v>
@@ -3305,27 +3371,27 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>73</v>
@@ -3335,27 +3401,27 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>73</v>
@@ -3365,24 +3431,24 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>54</v>
@@ -3395,10 +3461,10 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3406,16 +3472,16 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>73</v>
@@ -3425,10 +3491,10 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="J43" s="3">
         <v>2</v>
@@ -3436,16 +3502,16 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>73</v>
@@ -3455,24 +3521,24 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>54</v>
@@ -3480,29 +3546,31 @@
       <c r="E45" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>54</v>
@@ -3515,27 +3583,27 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>73</v>
@@ -3545,10 +3613,10 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="J47" s="3">
         <v>1</v>
@@ -3556,16 +3624,16 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>199</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>73</v>
@@ -3575,27 +3643,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>201</v>
+        <v>95</v>
       </c>
       <c r="J48" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>73</v>
@@ -3608,7 +3676,7 @@
         <v>205</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="J49" s="3">
         <v>1</v>
@@ -3616,13 +3684,13 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>206</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>54</v>
@@ -3641,21 +3709,21 @@
         <v>208</v>
       </c>
       <c r="J50" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>73</v>
@@ -3668,7 +3736,7 @@
         <v>211</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J51" s="3">
         <v>0</v>
@@ -3676,16 +3744,16 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>73</v>
@@ -3695,27 +3763,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>73</v>
@@ -3725,27 +3793,27 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>73</v>
@@ -3758,27 +3826,27 @@
         <v>218</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>219</v>
+        <v>95</v>
       </c>
       <c r="J54" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3788,21 +3856,21 @@
         <v>221</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>219</v>
+        <v>139</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>54</v>
@@ -3818,21 +3886,21 @@
         <v>224</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="J56" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>54</v>
@@ -3845,87 +3913,87 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>44</v>
+        <v>229</v>
       </c>
       <c r="J57" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>227</v>
+        <v>117</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>132</v>
+        <v>229</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="J59" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>73</v>
@@ -3935,24 +4003,24 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>54</v>
@@ -3960,31 +4028,29 @@
       <c r="E61" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>238</v>
-      </c>
+      <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="J61" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>241</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>54</v>
@@ -4000,21 +4066,21 @@
         <v>242</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="C63" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>54</v>
@@ -4027,10 +4093,10 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="J63" s="3">
         <v>3</v>
@@ -4038,29 +4104,29 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="C64" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J64" s="3">
         <v>0</v>
@@ -4068,19 +4134,19 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="C65" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
@@ -4090,27 +4156,27 @@
         <v>250</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D66" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
@@ -4120,111 +4186,111 @@
         <v>253</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="C67" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>201</v>
+        <v>99</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="D69" s="3" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>201</v>
+        <v>99</v>
       </c>
       <c r="J69" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>54</v>
@@ -4237,27 +4303,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>61</v>
+        <v>265</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>38</v>
@@ -4267,54 +4333,54 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="J71" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>54</v>
@@ -4327,120 +4393,120 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="J73" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="J74" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>201</v>
+        <v>95</v>
       </c>
       <c r="J75" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>219</v>
+        <v>139</v>
       </c>
       <c r="J76" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
@@ -4450,7 +4516,7 @@
         <v>283</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J77" s="3">
         <v>0</v>
@@ -4458,53 +4524,51 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="C78" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="C79" s="3" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>238</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
@@ -4512,21 +4576,21 @@
         <v>288</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>54</v>
@@ -4539,24 +4603,24 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>54</v>
@@ -4569,24 +4633,24 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>110</v>
+        <v>238</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>54</v>
@@ -4599,27 +4663,27 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="J82" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>296</v>
+        <v>172</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>73</v>
@@ -4629,10 +4693,10 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -4640,13 +4704,13 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>54</v>
@@ -4659,24 +4723,24 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>303</v>
+        <v>185</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>54</v>
@@ -4684,31 +4748,29 @@
       <c r="E85" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="I85" s="3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>306</v>
+        <v>117</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>54</v>
@@ -4721,24 +4783,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>110</v>
+        <v>307</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>54</v>
@@ -4751,10 +4813,10 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="J87" s="3">
         <v>1</v>
@@ -4762,13 +4824,13 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>309</v>
+        <v>117</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>54</v>
@@ -4781,10 +4843,10 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4792,13 +4854,13 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>54</v>
@@ -4811,27 +4873,27 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>313</v>
+        <v>238</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>314</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>303</v>
+        <v>190</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>73</v>
@@ -4844,24 +4906,24 @@
         <v>315</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="D91" s="3" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>73</v>
@@ -4874,10 +4936,10 @@
         <v>318</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="J91" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -4885,13 +4947,13 @@
         <v>319</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="D92" s="3" t="s">
-        <v>322</v>
+        <v>200</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>73</v>
@@ -4901,27 +4963,27 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>325</v>
+        <v>185</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>73</v>
@@ -4931,89 +4993,87 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="J93" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>265</v>
+        <v>325</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>328</v>
+        <v>252</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>332</v>
-      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>335</v>
+        <v>185</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>73</v>
@@ -5023,27 +5083,27 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="J96" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>335</v>
+        <v>193</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>73</v>
@@ -5053,152 +5113,154 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>265</v>
+        <v>335</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="J98" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c r="J99" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="C100" s="3" t="s">
-        <v>166</v>
+        <v>342</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>347</v>
+        <v>287</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>166</v>
+        <v>345</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>201</v>
+        <v>95</v>
       </c>
       <c r="J101" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="D102" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F102" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
@@ -5206,84 +5268,84 @@
         <v>351</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J102" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>353</v>
-      </c>
       <c r="C103" s="3" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="J103" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>227</v>
+        <v>355</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>163</v>
+        <v>345</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="J104" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>264</v>
+        <v>357</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>303</v>
-      </c>
       <c r="D105" s="3" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>73</v>
@@ -5296,7 +5358,7 @@
         <v>359</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J105" s="3">
         <v>0</v>
@@ -5310,10 +5372,10 @@
         <v>361</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>38</v>
@@ -5326,27 +5388,27 @@
         <v>362</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="J106" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>364</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
@@ -5356,24 +5418,24 @@
         <v>365</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>201</v>
+        <v>99</v>
       </c>
       <c r="J107" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>222</v>
+        <v>334</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>366</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>73</v>
@@ -5386,24 +5448,24 @@
         <v>367</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="J108" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="D109" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>73</v>
@@ -5416,14 +5478,284 @@
         <v>370</v>
       </c>
       <c r="I109" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J109" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I110" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J109" s="3">
+      <c r="J110" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J111" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J112" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J113" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J114" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J115" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J116" s="3">
         <v>1</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J117" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J118" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J109"/>
+  <autoFilter ref="A1:J118"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5533,6 +5865,15 @@
     <hyperlink ref="H107" r:id="rId106"/>
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5540,8 +5881,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5574,13 +5915,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5588,18 +5929,18 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5607,37 +5948,37 @@
         <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5645,18 +5986,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5664,18 +6005,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5683,18 +6024,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5702,18 +6043,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>117</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5721,18 +6062,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>246</v>
+        <v>117</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5740,18 +6081,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>117</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5759,18 +6100,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>271</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5778,18 +6119,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5797,18 +6138,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>288</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>295</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5816,18 +6157,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>298</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5835,18 +6176,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>300</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5854,18 +6195,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>166</v>
+        <v>282</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -5873,18 +6214,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>335</v>
+        <v>172</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5892,18 +6233,18 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>341</v>
+        <v>117</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -5911,18 +6252,18 @@
         <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>345</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>227</v>
+        <v>322</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -5930,18 +6271,18 @@
         <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -5949,18 +6290,18 @@
         <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>222</v>
+        <v>357</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>366</v>
+        <v>266</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>169</v>
+        <v>358</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -5968,11 +6309,68 @@
         <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>386</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G25"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5995,6 +6393,9 @@
     <hyperlink ref="G20" r:id="rId19"/>
     <hyperlink ref="G21" r:id="rId20"/>
     <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6008,15 +6409,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>238</v>
+        <v>397</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
@@ -6024,63 +6425,63 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>194</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>304</v>
+        <v>401</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>377</v>
+        <v>166</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -6088,31 +6489,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6120,7 +6521,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6128,10 +6529,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6150,7 +6551,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
@@ -6163,7 +6564,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>287</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -6179,7 +6580,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6187,15 +6588,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6203,7 +6604,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>299</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6211,15 +6612,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6227,7 +6628,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6235,7 +6636,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6243,7 +6644,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6251,7 +6652,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6259,7 +6660,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6267,7 +6668,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6288,16 +6689,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
@@ -6319,13 +6720,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3">
-        <v>17.5</v>
+        <v>14.0</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -6333,7 +6734,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3">
         <v>12.6</v>
@@ -6361,7 +6762,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C6" s="3">
         <v>11.3</v>
@@ -6378,10 +6779,10 @@
         <v>89</v>
       </c>
       <c r="C7" s="3">
-        <v>7.2</v>
+        <v>11.2</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6403,13 +6804,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="C9" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -6417,13 +6818,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>265</v>
+        <v>101</v>
       </c>
       <c r="C10" s="3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="D10" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6431,13 +6832,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>299</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>6.0</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6445,13 +6846,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="C12" s="3">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -6459,7 +6860,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C13" s="3">
         <v>2.9</v>
@@ -6473,10 +6874,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6487,7 +6888,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6501,7 +6902,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6527,15 +6928,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3">
         <v>3</v>
@@ -6549,10 +6950,10 @@
         <v>73</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4">
@@ -6560,10 +6961,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6582,7 +6983,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
@@ -6590,36 +6991,36 @@
         <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -6627,15 +7028,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6643,7 +7044,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6670,10 +7071,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6685,10 +7086,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6705,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>68</v>
@@ -6714,19 +7115,19 @@
         <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6737,28 +7138,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>44</v>
@@ -6769,31 +7170,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>303</v>
+        <v>193</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
@@ -6801,31 +7202,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>199</v>
+        <v>349</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="F5" s="3">
         <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
@@ -6833,31 +7234,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>412</v>
+        <v>347</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>255</v>
+        <v>348</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>413</v>
+        <v>349</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>415</v>
+        <v>351</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>208</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -6865,31 +7266,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>330</v>
+        <v>437</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>331</v>
+        <v>438</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>199</v>
+        <v>368</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="F7" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>333</v>
+        <v>441</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
@@ -6897,31 +7298,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>418</v>
+        <v>372</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>321</v>
+        <v>172</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9">
@@ -6929,31 +7330,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>423</v>
+        <v>209</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>166</v>
+        <v>349</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="F9" s="3">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -6961,31 +7362,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>241</v>
+        <v>448</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>166</v>
+        <v>282</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -6993,31 +7394,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="F11" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>208</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -7025,31 +7426,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>434</v>
+        <v>320</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13">
@@ -7057,28 +7458,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>166</v>
+        <v>462</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="F13" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7089,31 +7490,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>194</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -7121,31 +7522,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>447</v>
+        <v>147</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -7153,28 +7554,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>452</v>
+        <v>185</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7185,31 +7586,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>252</v>
+        <v>477</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>166</v>
+        <v>478</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="F17" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -7217,31 +7618,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>459</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>199</v>
+        <v>36</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -7249,31 +7650,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>140</v>
+        <v>485</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -7281,28 +7682,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -7313,28 +7714,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>470</v>
+        <v>372</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>471</v>
+        <v>172</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="F21" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W22.xlsx
+++ b/reports/devops-jobs-israel-2026-W22.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-28T10:21:13</t>
+    <t xml:space="preserve">2026-05-29T10:11:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6%</t>
+    <t xml:space="preserve">0.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -321,6 +321,21 @@
     <t xml:space="preserve">2026-05-28</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Engineer</t>
   </si>
   <si>
@@ -534,6 +549,15 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
@@ -543,6 +567,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
   </si>
   <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
@@ -552,6 +588,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
   </si>
   <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
+  </si>
+  <si>
     <t xml:space="preserve">SessionCam</t>
   </si>
   <si>
@@ -564,13 +609,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surpass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-surpass-4417658705</t>
   </si>
   <si>
     <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
@@ -582,160 +636,379 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloudride</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
   </si>
   <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finubit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-finubit-4420486202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-unilink-ltd-4419879717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - JB-652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grip Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, EWAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-ewaf-at-thales-4345712736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Sourcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-tim-sourcing-4420413333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Data Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-engineer-at-compie-technologies-4419815090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4420267483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4419075232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO NAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-senior-at-no-name-4407294836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4420669608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer (Cortex Research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-cortex-research-at-palo-alto-networks-4361488662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensi.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4419063857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-comblack-4420434265</t>
+  </si>
+  <si>
     <t xml:space="preserve">Harmonic</t>
   </si>
   <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417214194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grip Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4417624412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
+    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4419826411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; ML Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUNTHEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-ml-platform-engineer-at-hunthead-4417583856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-core-team-at-thales-4371458115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
   </si>
   <si>
     <t xml:space="preserve">Infotree Global Solutions</t>
@@ -744,49 +1017,10 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
   </si>
   <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4420235343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4419851508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4420267483</t>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer (Cloud Platform)</t>
@@ -795,55 +1029,64 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-platform-at-monday-com-4419824552</t>
   </si>
   <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-mobileye-4409774817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4415208513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer (620127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpearUAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-620127-at-spearuav-4417648068</t>
   </si>
   <si>
     <t xml:space="preserve">Lead SRE, DevOps Group</t>
@@ -855,567 +1098,243 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
   </si>
   <si>
-    <t xml:space="preserve">Mayfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-mayfield-4419119918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InspHire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Team Leader</t>
   </si>
   <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4419826411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - JB-652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sayari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Data Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-engineer-at-compie-technologies-4419815090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-unilink-ltd-4419879717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CRM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-crm-at-monday-com-4419805943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshed Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-eshed-group-4417626050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
+    <t xml:space="preserve">Netoplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-netoplay-4418933911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4418564684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentic DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empire Media Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/agentic-devops-at-empire-media-network-4418951731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4418249612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-malamteam-4392598255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4415208513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377765290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4414866213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InspHire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netoplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-netoplay-4418933911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator (36311)</t>
   </si>
   <si>
@@ -1473,30 +1392,36 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
   </si>
   <si>
-    <t xml:space="preserve">CAD Engineering - Student position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
   </si>
   <si>
@@ -1506,6 +1431,39 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1515,13 +1473,13 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1682,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
@@ -1690,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1698,7 +1656,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -1706,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1714,7 +1672,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1778,7 +1736,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -1786,7 +1744,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1805,36 +1763,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1842,7 +1800,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>421</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1861,130 +1819,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>406</v>
+        <v>364</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>398</v>
+        <v>489</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>503</v>
+        <v>382</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2009,13 +1967,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2">
@@ -2023,13 +1981,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3">
-        <v>12.5</v>
+        <v>14.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2038,88 +1996,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>37.7</v>
+        <v>35.4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.1</v>
+        <v>33.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.7</v>
+        <v>16.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2130,8 +2088,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2203,7 +2161,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2235,7 +2193,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2267,7 +2225,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2299,7 +2257,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -2331,7 +2289,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2363,7 +2321,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2395,7 +2353,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -2427,7 +2385,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2459,7 +2417,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -2491,7 +2449,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -2523,7 +2481,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -2555,7 +2513,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -2587,7 +2545,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -2619,7 +2577,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -2651,7 +2609,7 @@
         <v>44</v>
       </c>
       <c r="J16" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -2683,7 +2641,7 @@
         <v>95</v>
       </c>
       <c r="J17" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -2715,7 +2673,7 @@
         <v>99</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2726,13 +2684,13 @@
         <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>102</v>
@@ -2747,7 +2705,7 @@
         <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2755,68 +2713,68 @@
         <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="J21" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>113</v>
@@ -2825,7 +2783,7 @@
         <v>114</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>38</v>
@@ -2840,10 +2798,10 @@
         <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -2854,36 +2812,36 @@
         <v>118</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J23" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>54</v>
@@ -2894,90 +2852,90 @@
       <c r="E24" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>128</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>54</v>
@@ -2986,42 +2944,42 @@
         <v>54</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
@@ -3030,18 +2988,18 @@
         <v>138</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>53</v>
@@ -3050,30 +3008,30 @@
         <v>54</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="J29" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>53</v>
@@ -3085,36 +3043,36 @@
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>149</v>
@@ -3129,7 +3087,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -3137,10 +3095,10 @@
         <v>151</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>54</v>
@@ -3149,62 +3107,62 @@
         <v>73</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>54</v>
@@ -3213,89 +3171,89 @@
         <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>166</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>54</v>
@@ -3304,31 +3262,33 @@
         <v>54</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="J37" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>54</v>
@@ -3338,30 +3298,30 @@
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>73</v>
@@ -3371,10 +3331,10 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J39" s="3">
         <v>0</v>
@@ -3382,16 +3342,16 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>73</v>
@@ -3401,24 +3361,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>182</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>54</v>
@@ -3426,32 +3386,34 @@
       <c r="E41" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>73</v>
@@ -3461,27 +3423,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>73</v>
@@ -3491,27 +3453,27 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>73</v>
@@ -3521,56 +3483,54 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>194</v>
-      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>54</v>
@@ -3583,10 +3543,10 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J46" s="3">
         <v>0</v>
@@ -3594,16 +3554,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>200</v>
+        <v>54</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>73</v>
@@ -3613,10 +3573,10 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="J47" s="3">
         <v>1</v>
@@ -3624,16 +3584,16 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>200</v>
+        <v>54</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>73</v>
@@ -3643,24 +3603,24 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>54</v>
@@ -3673,24 +3633,24 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>54</v>
@@ -3703,27 +3663,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>200</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>73</v>
@@ -3733,27 +3693,27 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>200</v>
+        <v>54</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>73</v>
@@ -3763,10 +3723,10 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -3774,13 +3734,13 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>117</v>
+        <v>217</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>54</v>
@@ -3793,27 +3753,27 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="J53" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>73</v>
@@ -3823,54 +3783,54 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>54</v>
@@ -3883,54 +3843,54 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="J56" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>229</v>
+        <v>44</v>
       </c>
       <c r="J57" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>54</v>
@@ -3943,24 +3903,24 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>229</v>
+        <v>144</v>
       </c>
       <c r="J58" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>54</v>
@@ -3973,27 +3933,27 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>73</v>
@@ -4003,27 +3963,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>238</v>
+        <v>122</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>54</v>
+        <v>242</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>73</v>
@@ -4033,10 +3993,10 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="J61" s="3">
         <v>1</v>
@@ -4044,46 +4004,46 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>117</v>
+        <v>244</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>73</v>
@@ -4093,27 +4053,27 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>73</v>
@@ -4123,10 +4083,10 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J64" s="3">
         <v>0</v>
@@ -4134,106 +4094,106 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>248</v>
+        <v>122</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>61</v>
+        <v>254</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>252</v>
+        <v>180</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>117</v>
+        <v>257</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>172</v>
+        <v>261</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>54</v>
+        <v>242</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>73</v>
@@ -4243,27 +4203,27 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>258</v>
+        <v>122</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>73</v>
@@ -4273,24 +4233,24 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>54</v>
@@ -4303,57 +4263,57 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="J70" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>265</v>
+        <v>122</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>73</v>
@@ -4363,100 +4323,100 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="J75" s="3">
         <v>2</v>
@@ -4464,103 +4424,103 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>61</v>
+        <v>287</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>44</v>
+        <v>214</v>
       </c>
       <c r="J78" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>252</v>
+        <v>180</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>54</v>
@@ -4573,130 +4533,130 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="J79" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="J80" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>172</v>
+        <v>299</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -4704,73 +4664,73 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>299</v>
+        <v>61</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>225</v>
+        <v>44</v>
       </c>
       <c r="J84" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>302</v>
+        <v>65</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>117</v>
+        <v>307</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>54</v>
@@ -4783,24 +4743,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>54</v>
@@ -4813,27 +4773,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>117</v>
+        <v>314</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>185</v>
+        <v>316</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>73</v>
@@ -4843,10 +4803,10 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4854,16 +4814,16 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>312</v>
+        <v>122</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>172</v>
+        <v>261</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>54</v>
+        <v>242</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>73</v>
@@ -4873,27 +4833,27 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="J89" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>238</v>
+        <v>320</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>73</v>
@@ -4903,24 +4863,24 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>208</v>
+        <v>99</v>
       </c>
       <c r="J90" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>117</v>
+        <v>322</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>317</v>
+        <v>180</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>54</v>
@@ -4933,10 +4893,10 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="J91" s="3">
         <v>4</v>
@@ -4944,43 +4904,43 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>287</v>
+        <v>229</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>54</v>
@@ -4993,54 +4953,54 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>61</v>
+        <v>211</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="J94" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>54</v>
@@ -5053,24 +5013,24 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>54</v>
@@ -5083,27 +5043,27 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="J96" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>54</v>
+        <v>242</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>73</v>
@@ -5113,27 +5073,27 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="J97" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>73</v>
@@ -5143,27 +5103,27 @@
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>338</v>
+        <v>217</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>73</v>
@@ -5173,27 +5133,27 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="J99" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>342</v>
+        <v>183</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>73</v>
@@ -5203,43 +5163,43 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="J100" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>287</v>
+        <v>348</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J101" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -5247,105 +5207,103 @@
         <v>347</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>349</v>
+        <v>241</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>127</v>
+        <v>242</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>350</v>
-      </c>
+      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="J102" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>354</v>
+        <v>104</v>
       </c>
       <c r="J103" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>345</v>
+        <v>180</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>225</v>
+        <v>95</v>
       </c>
       <c r="J104" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>358</v>
+        <v>180</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>73</v>
@@ -5355,10 +5313,10 @@
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J105" s="3">
         <v>0</v>
@@ -5366,76 +5324,78 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F106" s="3"/>
+      <c r="F106" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="J106" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>364</v>
+        <v>241</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>127</v>
+        <v>242</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>73</v>
@@ -5445,27 +5405,27 @@
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>225</v>
+        <v>95</v>
       </c>
       <c r="J108" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>334</v>
+        <v>249</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>287</v>
+        <v>372</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>368</v>
+        <v>193</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>369</v>
+        <v>194</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>73</v>
@@ -5475,24 +5435,24 @@
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="J109" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>54</v>
@@ -5505,257 +5465,17 @@
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J110" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J111" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J112" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J113" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J114" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J115" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J116" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="J117" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J118" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
+  <autoFilter ref="A1:J110"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5866,14 +5586,6 @@
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
-    <hyperlink ref="H111" r:id="rId110"/>
-    <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
-    <hyperlink ref="H115" r:id="rId114"/>
-    <hyperlink ref="H116" r:id="rId115"/>
-    <hyperlink ref="H117" r:id="rId116"/>
-    <hyperlink ref="H118" r:id="rId117"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5881,8 +5593,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5915,13 +5627,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5929,56 +5641,56 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5986,18 +5698,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6005,18 +5717,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6024,18 +5736,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6043,18 +5755,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>117</v>
+        <v>249</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6062,18 +5774,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6081,18 +5793,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>117</v>
+        <v>272</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6100,18 +5812,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6119,18 +5831,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6138,18 +5850,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>251</v>
+        <v>305</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>252</v>
+        <v>180</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6157,18 +5869,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>253</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>117</v>
+        <v>314</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>193</v>
+        <v>316</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6176,18 +5888,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>255</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6195,18 +5907,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>261</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>280</v>
+        <v>353</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>281</v>
+        <v>354</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6214,18 +5926,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>283</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>297</v>
+        <v>359</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>233</v>
+        <v>360</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6233,18 +5945,18 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>298</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>362</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>310</v>
+        <v>363</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -6252,125 +5964,11 @@
         <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G19"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6390,12 +5988,6 @@
     <hyperlink ref="G17" r:id="rId16"/>
     <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
-    <hyperlink ref="G24" r:id="rId23"/>
-    <hyperlink ref="G25" r:id="rId24"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6409,15 +6001,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
@@ -6425,7 +6017,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3">
         <v>25</v>
@@ -6433,7 +6025,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="B4" s="3">
         <v>23</v>
@@ -6441,7 +6033,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B5" s="3">
         <v>21</v>
@@ -6449,7 +6041,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3">
         <v>18</v>
@@ -6457,7 +6049,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>401</v>
+        <v>171</v>
       </c>
       <c r="B7" s="3">
         <v>17</v>
@@ -6465,15 +6057,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>166</v>
+        <v>383</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="B9" s="3">
         <v>16</v>
@@ -6481,7 +6073,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -6489,7 +6081,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -6497,7 +6089,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -6505,15 +6097,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6521,7 +6113,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6529,7 +6121,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -6542,7 +6134,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6551,7 +6143,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
@@ -6564,15 +6156,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>287</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6580,23 +6172,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6604,7 +6196,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>229</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6612,7 +6204,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -6636,7 +6228,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6644,7 +6236,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6652,7 +6244,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6660,7 +6252,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6668,7 +6260,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6682,23 +6274,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
@@ -6720,7 +6312,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3">
         <v>14.0</v>
@@ -6734,7 +6326,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C4" s="3">
         <v>12.6</v>
@@ -6762,7 +6354,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C6" s="3">
         <v>11.3</v>
@@ -6804,13 +6396,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>287</v>
+        <v>106</v>
       </c>
       <c r="C9" s="3">
-        <v>7.0</v>
+        <v>6.2</v>
       </c>
       <c r="D9" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6818,10 +6410,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3">
-        <v>6.2</v>
+        <v>6.0</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -6832,13 +6424,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>229</v>
       </c>
       <c r="C11" s="3">
-        <v>6.0</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6846,13 +6438,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="C12" s="3">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6860,7 +6452,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C13" s="3">
         <v>2.9</v>
@@ -6874,10 +6466,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6888,7 +6480,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6902,7 +6494,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6928,18 +6520,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6950,10 +6542,10 @@
         <v>73</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4">
@@ -6964,7 +6556,7 @@
         <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -6983,7 +6575,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
@@ -6991,12 +6583,12 @@
         <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3">
         <v>10</v>
@@ -7004,10 +6596,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -7015,38 +6607,30 @@
         <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -7071,10 +6655,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7086,10 +6670,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -7106,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>68</v>
@@ -7115,19 +6699,19 @@
         <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7138,28 +6722,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>44</v>
@@ -7170,31 +6754,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>193</v>
+        <v>412</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
@@ -7202,31 +6786,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>349</v>
+        <v>180</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="F5" s="3">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
@@ -7234,31 +6818,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>420</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>349</v>
+        <v>180</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>351</v>
+        <v>423</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -7266,31 +6850,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="F7" s="3">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
@@ -7298,31 +6882,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>172</v>
+        <v>430</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>225</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -7330,31 +6914,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>209</v>
+        <v>265</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>349</v>
+        <v>180</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F9" s="3">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>229</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10">
@@ -7362,31 +6946,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F10" s="3">
+        <v>48</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -7394,28 +6978,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>452</v>
+        <v>152</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7426,31 +7010,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>225</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -7458,28 +7042,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7490,31 +7074,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>466</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>349</v>
+        <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F14" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -7522,28 +7106,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>147</v>
+        <v>363</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7554,28 +7138,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7586,28 +7170,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>478</v>
+        <v>203</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7618,28 +7202,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>35</v>
+        <v>282</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7650,31 +7234,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="F19" s="3">
+        <v>36</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -7682,31 +7266,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21">
@@ -7714,31 +7298,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W22.xlsx
+++ b/reports/devops-jobs-israel-2026-W22.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-29T10:11:46</t>
+    <t xml:space="preserve">2026-05-31T09:17:29</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9%</t>
+    <t xml:space="preserve">1.7%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -438,915 +438,1011 @@
     <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Group Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stampli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stampli-4422563145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4415246112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – Cloud &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-cloud-infrastructure-at-michal-recruiting-placement-4421333933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4420959611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surpass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-surpass-4417658705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4421345951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CRM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-crm-at-monday-com-4419805943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4418360624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4417624412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-corsa-4419470455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4420267483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4409726747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4417616930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4409576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4416809451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentic DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empire Media Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/agentic-devops-at-empire-media-network-4418951731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4419826411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finubit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-finubit-4420486202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-gong-4418991840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-mobileye-4409774817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-comblack-4420434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - JB-652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 50% Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-50%25-position-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4419075232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Cloud Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-platform-at-monday-com-4419824552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4418355841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-unilink-ltd-4419879717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-native-4418239509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-apple-4421047611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-electreon-4417590705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud Infrastructure Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, Linux, Python, CDK, Networking, Security, FinOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7747977003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Group Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablemen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4420401522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4409847610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-native-4418238573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4415295209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4419100325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surpass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-surpass-4417658705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone Solutions &amp; Strategy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-keystone-solutions-strategy-4417211326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudride-4417208573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4417628977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sayari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sayari-4418671532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4420400643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finubit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-finubit-4420486202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-unilink-ltd-4419879717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - JB-652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-jb-652-at-pwc-next-technology-solutions-4418670511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4415293915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4418947261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-toluna-4417610759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grip Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-data-platform-engineer-at-grip-security-4408224592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, EWAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-ewaf-at-thales-4345712736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Sourcing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-tim-sourcing-4420413333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Data Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-engineer-at-compie-technologies-4419815090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Architect (25000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25000-at-yael-group-4417626508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4420267483</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-axonius-4416885853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4418249612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4415208513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-malamteam-4392598255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer (620127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpearUAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-620127-at-spearuav-4417648068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4418386111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
   </si>
   <si>
     <t xml:space="preserve">Wiz</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4419075232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Senior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-senior-at-no-name-4407294836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4420669608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (New Ventures)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-new-ventures-at-monday-com-4419814790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Be'er Sheva)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-be-er-sheva-at-cyberark-4378443169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer (Cortex Research)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-cortex-research-at-palo-alto-networks-4361488662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensi.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4419063857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-shavit-software-4419189010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DATA Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-comblack-4420434265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4419826411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; ML Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUNTHEAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-ml-platform-engineer-at-hunthead-4417583856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-core-team-at-thales-4371458115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Cloud Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-platform-at-monday-com-4419824552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4388077081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418916930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4415208513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer (620127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpearUAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-620127-at-spearuav-4417648068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4417885268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InspHire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netoplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-netoplay-4418933911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4418564684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agentic DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empire Media Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/agentic-devops-at-empire-media-network-4418951731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
@@ -1356,9 +1452,6 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Outpost24</t>
   </si>
   <si>
@@ -1401,25 +1494,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
@@ -1443,27 +1524,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
   </si>
   <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1476,10 +1536,10 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1640,7 +1700,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -1648,7 +1708,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1656,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1664,7 +1724,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>375</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10">
@@ -1672,7 +1732,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1736,7 +1796,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -1744,7 +1804,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1763,15 +1823,15 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -1779,30 +1839,22 @@
         <v>431</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="B6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1819,15 +1871,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="B2" s="3">
         <v>57</v>
@@ -1835,47 +1887,47 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>384</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>484</v>
+        <v>409</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
@@ -1883,15 +1935,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="B10" s="3">
         <v>16</v>
@@ -1899,39 +1951,39 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>489</v>
+        <v>405</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -1939,10 +1991,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>382</v>
+        <v>509</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1967,13 +2019,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2">
@@ -1981,13 +2033,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1996,88 +2048,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3">
-        <v>35.4</v>
+        <v>39.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.6</v>
+        <v>93.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.5</v>
+        <v>20.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.2</v>
+        <v>13.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2161,7 +2213,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -2193,7 +2245,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2225,7 +2277,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2309,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -2289,7 +2341,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -2321,7 +2373,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2353,7 +2405,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -2385,7 +2437,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -2417,7 +2469,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -2449,7 +2501,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2533,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -2513,7 +2565,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -2545,7 +2597,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2577,7 +2629,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -2609,7 +2661,7 @@
         <v>44</v>
       </c>
       <c r="J16" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -2641,7 +2693,7 @@
         <v>95</v>
       </c>
       <c r="J17" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -2673,7 +2725,7 @@
         <v>99</v>
       </c>
       <c r="J18" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2705,7 +2757,7 @@
         <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2737,7 +2789,7 @@
         <v>109</v>
       </c>
       <c r="J20" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2769,7 +2821,7 @@
         <v>99</v>
       </c>
       <c r="J21" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2801,7 +2853,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -2833,7 +2885,7 @@
         <v>109</v>
       </c>
       <c r="J23" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -2865,7 +2917,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -2895,7 +2947,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2927,7 +2979,7 @@
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -2959,7 +3011,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -2991,7 +3043,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -3008,27 +3060,27 @@
         <v>54</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>140</v>
@@ -3043,36 +3095,36 @@
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D31" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>149</v>
@@ -3087,7 +3139,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -3095,10 +3147,10 @@
         <v>151</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>54</v>
@@ -3107,62 +3159,62 @@
         <v>73</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>54</v>
@@ -3171,90 +3223,90 @@
         <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>163</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J35" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="J36" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="C37" s="3" t="s">
         <v>54</v>
       </c>
@@ -3262,33 +3314,31 @@
         <v>54</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>54</v>
@@ -3298,16 +3348,16 @@
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="J38" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -3315,10 +3365,10 @@
         <v>122</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>54</v>
@@ -3331,89 +3381,87 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>184</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>73</v>
@@ -3423,27 +3471,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>54</v>
+        <v>188</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>73</v>
@@ -3453,13 +3501,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -3467,13 +3515,13 @@
         <v>122</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>194</v>
+        <v>37</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>73</v>
@@ -3483,13 +3531,13 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -3497,10 +3545,10 @@
         <v>122</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>132</v>
@@ -3513,24 +3561,24 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>54</v>
@@ -3543,10 +3591,10 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="J46" s="3">
         <v>0</v>
@@ -3557,10 +3605,10 @@
         <v>122</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>54</v>
@@ -3573,13 +3621,13 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3587,13 +3635,13 @@
         <v>122</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>73</v>
@@ -3603,24 +3651,24 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>54</v>
@@ -3628,18 +3676,20 @@
       <c r="E49" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3647,10 +3697,10 @@
         <v>122</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>54</v>
@@ -3663,24 +3713,24 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>54</v>
@@ -3693,13 +3743,13 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="J51" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3707,13 +3757,13 @@
         <v>122</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>73</v>
@@ -3723,10 +3773,10 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -3734,13 +3784,13 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>217</v>
+        <v>122</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>54</v>
@@ -3753,13 +3803,13 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -3767,10 +3817,10 @@
         <v>122</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>54</v>
@@ -3783,24 +3833,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>222</v>
+        <v>122</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>54</v>
@@ -3813,24 +3863,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>122</v>
+        <v>222</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>54</v>
@@ -3843,73 +3893,73 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="J57" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3917,10 +3967,10 @@
         <v>122</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>54</v>
@@ -3933,13 +3983,13 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="J59" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3947,13 +3997,13 @@
         <v>122</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>73</v>
@@ -3963,10 +4013,10 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J60" s="3">
         <v>3</v>
@@ -3974,119 +4024,119 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>122</v>
+        <v>235</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>242</v>
+        <v>54</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>244</v>
+        <v>122</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="J62" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>132</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>249</v>
+        <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="J64" s="3">
         <v>0</v>
@@ -4097,10 +4147,10 @@
         <v>122</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>54</v>
@@ -4113,27 +4163,27 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>73</v>
@@ -4143,24 +4193,24 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>54</v>
@@ -4173,43 +4223,43 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>261</v>
+        <v>175</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>242</v>
+        <v>54</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
@@ -4217,10 +4267,10 @@
         <v>122</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>54</v>
@@ -4233,24 +4283,24 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>122</v>
+        <v>257</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>54</v>
@@ -4258,29 +4308,31 @@
       <c r="E70" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>122</v>
+        <v>260</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>54</v>
@@ -4293,27 +4345,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>270</v>
+        <v>175</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>73</v>
@@ -4323,84 +4375,84 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>193</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>54</v>
@@ -4413,24 +4465,24 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>54</v>
@@ -4443,84 +4495,84 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="J77" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>214</v>
+        <v>99</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>289</v>
+        <v>122</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>285</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>54</v>
@@ -4533,10 +4585,10 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>60</v>
+        <v>228</v>
       </c>
       <c r="J79" s="3">
         <v>4</v>
@@ -4544,103 +4596,103 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>292</v>
+        <v>226</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>298</v>
+        <v>226</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>301</v>
+        <v>65</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>54</v>
@@ -4653,24 +4705,24 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>54</v>
@@ -4683,54 +4735,54 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="J84" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>307</v>
+        <v>122</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>309</v>
+        <v>175</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>54</v>
@@ -4743,24 +4795,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J86" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>54</v>
@@ -4773,27 +4825,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>316</v>
+        <v>200</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>73</v>
@@ -4803,27 +4855,27 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>122</v>
+        <v>309</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>73</v>
@@ -4833,10 +4885,10 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="J89" s="3">
         <v>2</v>
@@ -4844,16 +4896,16 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>320</v>
+        <v>122</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>180</v>
+        <v>313</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>54</v>
+        <v>314</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>73</v>
@@ -4863,24 +4915,24 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>54</v>
@@ -4893,10 +4945,10 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>60</v>
+        <v>228</v>
       </c>
       <c r="J91" s="3">
         <v>4</v>
@@ -4904,46 +4956,46 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>229</v>
+        <v>320</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>203</v>
+        <v>324</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>73</v>
@@ -4953,10 +5005,10 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>214</v>
+        <v>95</v>
       </c>
       <c r="J93" s="3">
         <v>5</v>
@@ -4964,16 +5016,16 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>211</v>
+        <v>316</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>73</v>
@@ -4983,10 +5035,10 @@
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="J94" s="3">
         <v>2</v>
@@ -4994,13 +5046,13 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>234</v>
+        <v>330</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>54</v>
@@ -5013,24 +5065,24 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J95" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>54</v>
@@ -5043,54 +5095,54 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="J96" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>337</v>
+        <v>190</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>338</v>
+        <v>175</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>242</v>
+        <v>54</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="J97" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>217</v>
+        <v>122</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>54</v>
@@ -5103,24 +5155,24 @@
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J98" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>217</v>
+        <v>122</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>203</v>
+        <v>274</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>54</v>
@@ -5133,24 +5185,24 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J99" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>344</v>
+        <v>122</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>54</v>
@@ -5163,27 +5215,27 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="J100" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>347</v>
+        <v>122</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>132</v>
+        <v>314</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>73</v>
@@ -5193,27 +5245,27 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J101" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>347</v>
+        <v>122</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>242</v>
+        <v>314</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>73</v>
@@ -5223,10 +5275,10 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>214</v>
+        <v>95</v>
       </c>
       <c r="J102" s="3">
         <v>5</v>
@@ -5234,13 +5286,13 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>354</v>
+        <v>184</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>54</v>
@@ -5248,59 +5300,61 @@
       <c r="E103" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F103" s="3"/>
+      <c r="F103" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="J103" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>356</v>
+        <v>289</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J104" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>54</v>
@@ -5313,42 +5367,40 @@
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="J105" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>364</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="J106" s="3">
         <v>0</v>
@@ -5356,46 +5408,46 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>241</v>
+        <v>358</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="J107" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>241</v>
+        <v>361</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>73</v>
@@ -5405,77 +5457,411 @@
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>95</v>
+        <v>363</v>
       </c>
       <c r="J108" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>249</v>
+        <v>364</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>193</v>
+        <v>366</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>73</v>
+        <v>367</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="J109" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>309</v>
+        <v>203</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F110" s="3"/>
+      <c r="F110" s="3" t="s">
+        <v>371</v>
+      </c>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J110" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J111" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="I112" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J112" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J113" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J114" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J115" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J116" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J117" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I119" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J110" s="3">
-        <v>3</v>
+      <c r="J119" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J120" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J121" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J110"/>
+  <autoFilter ref="A1:J121"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5586,6 +5972,17 @@
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5593,8 +5990,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5627,32 +6024,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5660,7 +6057,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
@@ -5668,10 +6065,10 @@
         <v>122</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5679,7 +6076,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -5687,10 +6084,10 @@
         <v>122</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5698,7 +6095,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
@@ -5706,10 +6103,10 @@
         <v>122</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5717,18 +6114,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5736,18 +6133,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>247</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5755,18 +6152,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>249</v>
+        <v>122</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5774,18 +6171,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5793,18 +6190,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>272</v>
+        <v>122</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5812,18 +6209,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5831,18 +6228,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>295</v>
+        <v>180</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5850,18 +6247,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5869,18 +6266,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>315</v>
+        <v>190</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>316</v>
+        <v>175</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5888,18 +6285,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>229</v>
+        <v>355</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5907,15 +6304,15 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>203</v>
@@ -5926,18 +6323,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5945,18 +6342,18 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -5964,11 +6361,30 @@
         <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>365</v>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G20"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5988,6 +6404,7 @@
     <hyperlink ref="G17" r:id="rId16"/>
     <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6001,31 +6418,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>379</v>
+        <v>206</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="B4" s="3">
         <v>23</v>
@@ -6033,23 +6450,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>382</v>
+        <v>166</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>171</v>
+        <v>407</v>
       </c>
       <c r="B7" s="3">
         <v>17</v>
@@ -6057,23 +6474,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -6081,31 +6498,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6113,7 +6530,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6121,10 +6538,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6134,7 +6551,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6143,7 +6560,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
@@ -6164,7 +6581,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6172,15 +6589,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6188,7 +6605,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6196,7 +6613,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>229</v>
+        <v>140</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6204,7 +6621,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>279</v>
+        <v>180</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -6212,15 +6629,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6228,7 +6645,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6236,7 +6653,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6244,7 +6661,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>265</v>
+        <v>184</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6252,7 +6669,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6260,7 +6677,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6281,16 +6698,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
@@ -6312,7 +6729,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3">
         <v>14.0</v>
@@ -6326,13 +6743,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6340,13 +6757,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C5" s="3">
-        <v>12.5</v>
+        <v>11.3</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6354,10 +6771,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="C6" s="3">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6368,10 +6785,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="C7" s="3">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
@@ -6424,13 +6841,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C11" s="3">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -6438,10 +6855,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>279</v>
+        <v>180</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -6452,13 +6869,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6466,10 +6883,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6480,13 +6897,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>265</v>
+        <v>123</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6494,10 +6911,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6520,18 +6937,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>141</v>
+        <v>367</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6542,10 +6959,10 @@
         <v>73</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4">
@@ -6553,10 +6970,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -6575,7 +6992,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2">
@@ -6583,7 +7000,7 @@
         <v>54</v>
       </c>
       <c r="B2" s="3">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -6591,28 +7008,28 @@
         <v>132</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>242</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6620,7 +7037,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6643,7 +7060,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6655,10 +7072,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6670,10 +7087,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6690,7 +7107,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>68</v>
@@ -6699,19 +7116,19 @@
         <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6722,31 +7139,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -6754,31 +7171,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>412</v>
+        <v>187</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
@@ -6786,31 +7203,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>282</v>
+        <v>370</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="F5" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6">
@@ -6818,31 +7235,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>419</v>
+        <v>369</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>420</v>
+        <v>370</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -6850,31 +7267,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>338</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
@@ -6882,31 +7299,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>429</v>
+        <v>261</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>430</v>
+        <v>175</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
@@ -6914,31 +7331,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>265</v>
+        <v>452</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="F9" s="3">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>437</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -6946,31 +7363,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>316</v>
+        <v>175</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="F10" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -6978,31 +7395,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>152</v>
+        <v>461</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>153</v>
+        <v>462</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>402</v>
+        <v>445</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -7010,28 +7427,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>203</v>
+        <v>467</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -7042,31 +7459,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>451</v>
+        <v>175</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>44</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14">
@@ -7074,28 +7491,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7106,28 +7523,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>363</v>
+        <v>477</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7138,28 +7555,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>180</v>
+        <v>482</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7170,28 +7587,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>464</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7202,28 +7619,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>282</v>
+        <v>399</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F18" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7234,31 +7651,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F19" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
@@ -7266,31 +7683,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>475</v>
+        <v>261</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>437</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -7298,31 +7715,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>480</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
